--- a/Intro-Math-Programming/baseText/book/Figures-and-AltText-book1-filled.xlsx
+++ b/Intro-Math-Programming/baseText/book/Figures-and-AltText-book1-filled.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="E2" s="17" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F2" s="17" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="E3" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>A hierarchical classification of optimization models showing Convex models and Non-convex models as subcategories. A linear programming visualization showing a light blue hexagonal feasible region with labeled vertices, an objective direction arrow, and a red objective function line.</t>
+          <t>Tree diagram classifying optimization models. The root 'Optimization Models' splits into Linear and Nonlinear branches, which each split by variable type (continuous vs integer) into four leaves: LP (polynomial time), MILP (NP-hard), NLP (varies), and MINLP (NP-hard). A linear programming visualization showing a light blue hexagonal feasible region with labeled vertices, an objective direction arrow, and a red objective function line.</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F6" s="18" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F7" s="18" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F9" s="18" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F12" s="18" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F15" s="18" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F16" s="18" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>Feasible region shaded blue with vertices (0,0), (0,7), (4,5), (7,2), (8,0); parallel red level lines x+y=7, x+y=9, and x+y=10 sweep across the region, with a green line 2x+y=16 and a brown line showing a modified constraint. Sensitivity analysis visualization showing how the optimal solution changes as objective function coefficients vary. A Microsoft Excel Solver Results dialog box showing a successful optimization, with options to keep the solution or restore original values, and report type selections. An Excel spreadsheet setup for a linear programming problem with decision variables in yellow cells. Constraints are defined with coefficients, totals, and right-hand side values.</t>
+          <t>Feasible region shaded blue with vertices (0,0), (0,7), (4,5), (7,2), (8,0); parallel red level lines x+y=7, x+y=9, and x+y=10 sweep across the region, with a green line 2x+y=16 and a brown line showing a modified constraint. Feasible region in the x-y plane with several level curves of the objective z = c_x x + 3y drawn for different slopes. The figure shows that as long as c_x lies in the interval [1.5, 3], the level curves tilt within the cone defined by the active constraints at the current optimum, so the optimal vertex (and basis) does not change. Screenshot of Excel's Solver Results dialog with the option to generate a Sensitivity report selected, illustrating how to request post-optimal sensitivity output after solving a linear program. Screenshot of an Excel worksheet set up for a linear program: decision-variable cells, an objective-function cell using SUMPRODUCT, and constraint left-hand-side formulas alongside their right-hand-side values, ready for Solver.</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>A Microsoft Excel Solver sensitivity analysis report showing Variable Cells and Constraints sections with columns for Final Value, Reduced Cost, and Shadow Price.</t>
+          <t>Screenshot of an Excel Solver sensitivity report. The Variable Cells table lists each decision variable's final value, reduced cost, objective coefficient, and allowable increase/decrease; the Constraints table lists each constraint's final value, shadow price, RHS, and allowable increase/decrease, identifying binding versus non-binding constraints.</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F26" s="18" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>Graph showing an inventory risk function where risk cost increases rapidly and asymptotically approaches a maximum as inventory level increases.</t>
+          <t>Plot of the inventory risk function r(s) = c_r(1 - exp(-beta*s)) versus inventory level s: a smooth concave curve rising sharply from zero and saturating toward the maximum risk cost c_r, illustrating that marginal risk diminishes as inventory grows.</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>A Pareto front curve showing the trade-off between Total Cost and Maximum Risk Cost, demonstrating diminishing returns as one objective improves at the expense of the other.</t>
+          <t>Pareto frontier curve for the multi-objective inventory problem, plotting total cost (horizontal axis) against maximum inventory risk (vertical axis). The downward-sloping non-dominated trade-off curve shows that lower risk can only be achieved by accepting higher cost.</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
         </is>
       </c>
       <c r="F35" s="18" t="inlineStr">
@@ -1891,421 +1891,5286 @@
       <c r="H41" s="18" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="B42" s="13" t="n"/>
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP1)</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot of the line y = 3x + 2 on x-y axes with a gridded background. Three labelled points (-1,-1), (0,2), and (1,5) lie on a blue line of slope 3 with y-intercept 2.</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="B43" s="13" t="n"/>
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP1)</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot of the line 2x + y = 4 on gridded x-y axes. A blue line passes through three labelled points (-1,6), (0,4), and (1,2), illustrating slope -2 and y-intercept 4.</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="B44" s="13" t="n"/>
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP1)</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="B45" s="13" t="n"/>
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP1)</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="B46" s="13" t="n"/>
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP1)</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot of the horizontal line y = 3 on gridded x-y axes. The blue line is drawn parallel to the x-axis through the labelled y-intercept (0,3).</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="B47" s="13" t="n"/>
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP1)</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot of the vertical line x = -2 on gridded x-y axes. The blue line is drawn parallel to the y-axis through the labelled x-intercept (-2,0).</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="B48" s="13" t="n"/>
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP1)</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot illustrating the slope of the line through (-2,3) and (4,-1) on x-y axes. A blue line connects the two labelled points; green arrows mark a vertical drop of -4 and a horizontal run of 6, giving slope -2/3.</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="B49" s="13" t="n"/>
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP1)</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot of the line through (1,2) with slope -3/4 on gridded x-y axes. A blue line passes through the labelled points (1,2) and (5,-1); green arrows indicate a vertical change of -3 and horizontal change of 4.</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="B50" s="13" t="n"/>
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP1)</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot of an equilibrium point. The blue upward supply line y = 3.5x - 14 and the red downward demand line y = -2.5x + 34 intersect at the labelled green point (8,14), with dashed lines dropping to Quantity = 8 and Price = 14.</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="B51" s="13" t="n"/>
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP1)</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot of a break-even point. The blue revenue line R = 5x and the red cost line C = 3x + 12 intersect at the labelled green point (6,30), with dashed lines marking Quantity = 6 and Cost/Revenue = 30.</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="B52" s="13" t="n"/>
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP2)</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Three side-by-side 2D plots showing how two lines can intersect: 'One Solution' (crossing at a single point), 'No Solutions' (parallel lines), and 'Infinitely Many Solutions' (a single line representing two coincident equations).</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="B53" s="13" t="n"/>
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP2)</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot of the system x+y=3 and y-x=5: a green line and a blue line crossing at the labelled point (x,y) = (-1,4), with helper lines dropped to the x- and y-axes to show the unique solution.</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G53" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="B54" s="13" t="n"/>
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP2)</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>Two side-by-side two-dimensional plots showing three lines in the plane: on the left, three lines that pairwise intersect but share no common point ('No Solution'); on the right, three lines all passing through a single marked point ('One Solution').</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="B55" s="13" t="n"/>
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP2)</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>PICT</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="B56" s="13" t="n"/>
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP2)</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>PICT</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="B57" s="13" t="n"/>
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP2)</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>PICT</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="B58" s="13" t="n"/>
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP2)</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>PICT</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="B59" s="13" t="n"/>
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot of the xy-plane showing two points P = (2,1) and Q = (-3,4) marked as red dots, with light helper lines dropped to the axes to indicate each point's coordinates.</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="B60" s="13" t="n"/>
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>Three-dimensional diagram of the position vector 0P: a thick blue arrow from the origin along the x-, y-, z-axes to a red point P=(p_1,p_2,p_3), labelled with the column-vector form [p_1,p_2,p_3]^T.</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="B61" s="13" t="n"/>
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>Three-dimensional diagram with two parallel blue arrows of equal length and direction: the position vector 0P from the origin and a translated copy AB from point A to point B, illustrating that translating a vector preserves its identity.</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G61" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="B62" s="13" t="n"/>
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional vector diagram illustrating the tip-to-tail rule for vector addition: arrow u along the x-axis, arrow v starting at the tip of u and going to the upper right, and a third arrow from the tail of u to the tip of v labelled u+v.</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="B63" s="13" t="n"/>
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>PICT</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="B64" s="13" t="n"/>
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional sketch of vectors u (blue, up and right) and v (red, down and right) drawn as separate arrows, presented as the setup for graphing the linear combinations u+2v and u-1/2 v.</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="B65" s="13" t="n"/>
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional vector diagram of u+v drawn tip-to-tail: blue u from the origin to the upper right, red v continuing from the tip of u, and the purple resultant u+v drawn from the tail of u to the tip of v.</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="B66" s="13" t="n"/>
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional vector diagram of u-v: blue u from the origin, red -v starting at the tip of u and pointing in the reverse direction of v, and a purple arrow from the origin to the tip of -v representing u-v=u+(-v).</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="B67" s="13" t="n"/>
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>PICT</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H67" s="18" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="B68" s="13" t="n"/>
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>PICT</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="B69" s="13" t="n"/>
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional sketch of vectors u (blue, up and right) and v (red, down and right) drawn as separate arrows, presented as the setup for graphing the linear combinations u+2v and u-1/2 v.</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="B70" s="13" t="n"/>
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional diagram showing scalar multiples of two vectors: blue vector u and its negative -u (same length, opposite direction), plus red vector v together with 2v (twice as long, same direction) and -1/2 v (half-length, reversed).</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="B71" s="13" t="n"/>
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional sketch of vectors u (blue, up and right) and v (red, down and right) drawn as separate arrows, presented as the setup for graphing the linear combinations u+2v and u-1/2 v.</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="B72" s="13" t="n"/>
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional vector diagram of the linear combination u + 2v: blue vector u from the origin, red vector 2v drawn tip-to-tail starting at u's head, and the purple resultant u+2v from the origin to the final tip.</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H72" s="18" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="B73" s="13" t="n"/>
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional vector diagram of the linear combination u - 1/2 v: blue u from the origin, the short red vector -1/2 v placed tip-to-tail at u's head, and the purple resultant u - 1/2 v drawn from the origin to the final tip.</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H73" s="18" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="B74" s="13" t="n"/>
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (AP4)</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional sketch of two vectors emanating from a common origin: a blue vector v pointing up and to the right and a red vector u pointing down and to the right, with the included angle theta marked between them.</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H74" s="18" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="B75" s="13" t="n"/>
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>Aerial photograph of a Missoula, Montana housing development showing several blocks of houses connected by a network of streets. The image motivates the question of whether a lawn inspector can walk every street without backtracking.</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>David Lippman, Math in Society [CC BY-SA 3.0]; aerial base image by Sam Beebe [CC BY]. Graphpicture</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>David Lippman, Math in Society [CC BY-SA 3.0]; aerial base image by Sam Beebe [CC BY], “Graphpicture”, CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="B76" s="13" t="n"/>
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>Side-by-side: the housing aerial photo is overlaid with red dots at intersections and red lines along streets; next to it, the same network is redrawn as a graph of labeled vertices joined by edges, showing the reduction of a street map to a graph.</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>David Lippman, Math in Society [CC BY-SA 3.0]; aerial base image by Sam Beebe [CC BY]. Graphpicturedot</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>David Lippman, Math in Society [CC BY-SA 3.0]; aerial base image by Sam Beebe [CC BY], “Graphpicturedot”, CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="B77" s="13" t="n"/>
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>Eighteen-vertex housing-development graph with nodes A through R laid out on a roughly grid-like map of streets; reused from earlier in the chapter to ask whether an Euler circuit exists for the lawn inspector.</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G77" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H77" s="18" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="B78" s="13" t="n"/>
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>The same 18-vertex graph G (vertices A through R) redrawn with vertices scattered in a non-grid layout. The edge set is identical to the previous figure, illustrating that a graph's structure is independent of how it is drawn.</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H78" s="18" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="B79" s="13" t="n"/>
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>Historical map of the Prussian city of Koenigsberg with the river highlighted in blue and the seven bridges that cross its forks marked in green, depicting the geographic setting of the famous Koenigsberg bridge problem that launched graph theory.</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>Bogdan Giusca [CC BY-SA 3.0], via Wikimedia Commons. Konigsberg Bridges</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>Bogdan Giusca [CC BY-SA 3.0], via Wikimedia Commons, “Konigsberg Bridges”, CC BY-SA 3.0, https://commons.wikimedia.org/wiki/File:Konigsberg_bridges.png</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H79" s="18" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="B80" s="13" t="n"/>
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>Schematic of Konigsberg's four landmasses drawn as labelled ellipses (North Bank, Island, East Bank, South Bank) with seven short line segments crossing between them representing the seven bridges of the puzzle.</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="B81" s="13" t="n"/>
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>Graph abstraction of the Konigsberg bridges: four circular vertices labelled NB, I, EB, and SB with seven edges connecting them, including two parallel arcs between NB and I and two between I and SB to represent the duplicate bridges (a multigraph).</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="B82" s="13" t="n"/>
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>Small graph illustrating a loop: three filled-dot vertices form a triangle and a red self-loop attaches to the rightmost vertex, showing an edge that connects a vertex to itself.</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H82" s="18" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="B83" s="13" t="n"/>
+      <c r="A83" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>Single isolated vertex with no edges, illustrating a vertex of degree 0 in the table of degree examples.</t>
+        </is>
+      </c>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H83" s="18" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="B84" s="13" t="n"/>
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>A vertex with one edge attached, illustrating degree 1 in the table of degree examples.</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="B85" s="13" t="n"/>
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>A vertex with two edges attached (forming a V), illustrating degree 2 in the table of degree examples.</t>
+        </is>
+      </c>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H85" s="18" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="B86" s="13" t="n"/>
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>A vertex with three edges attached, illustrating degree 3 in the table of degree examples.</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H86" s="18" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="B87" s="13" t="n"/>
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>A vertex with four edges attached (one to each diagonal direction), illustrating degree 4 in the table of degree examples.</t>
+        </is>
+      </c>
+      <c r="D87" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H87" s="18" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="B88" s="13" t="n"/>
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>A 3-by-4 grid graph with 12 vertices labelled A-D (top), E-H (middle), J-M (bottom). All grid edges are drawn; a path from A to M is highlighted in thick red, traversing A-E-F-G-L-M.</t>
+        </is>
+      </c>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H88" s="18" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="B89" s="13" t="n"/>
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>The same 3-by-4 grid graph (vertices A-D, E-H, J-M) with a circuit highlighted in thick red, beginning and ending at vertex A by traversing A-E-J-K-F-B-A and similar back path, illustrating a cycle.</t>
+        </is>
+      </c>
+      <c r="D89" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G89" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H89" s="18" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="B90" s="13" t="n"/>
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>A 3-by-4 grid graph with vertices A-D, E-H, J-M, but with the column-A horizontal edges deleted so that vertex A and the left column are isolated from the rest, illustrating a disconnected graph.</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G90" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="B91" s="13" t="n"/>
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>Weighted graph of five U.S. cities (LA, Seattle, Chicago, Atlanta, Dallas) shown as filled dots arranged across the plane, with all ten edges drawn and labelled with one-way airfares such as $70 (LA-Seattle), $150 (LA-Dallas), $85 (Atlanta-Dallas), $75 (Chicago-Atlanta).</t>
+        </is>
+      </c>
+      <c r="D91" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F91" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G91" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="B92" s="13" t="n"/>
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>Initial-state diagram for Dijkstra's algorithm: seven blue circular nodes T, E, A, NB, MR, P, Y connected by weighted edges (e.g., T-A=20, A-NB=36, NB-Y=120, MR-Y=90); each node has a green-boxed tentative-distance label, all set to infinity except the destination T which is 0.</t>
+        </is>
+      </c>
+      <c r="D92" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G92" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H92" s="18" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="B93" s="13" t="n"/>
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>Weighted road network for the Yakima-to-Tacoma example: seven filled-dot vertices T (Tacoma), E (Eatonville), A (Auburn), NB (North Bend), MR (Mount Rainier), P (Packwood), Y (Yakima) with edges labelled by travel times in minutes (e.g., T-A=20, A-NB=36, NB-Y=104, MR-Y=96, P-Y=76).</t>
+        </is>
+      </c>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G93" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H93" s="18" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="B94" s="13" t="n"/>
+      <c r="A94" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>Yakima-to-Tacoma road network as before, now with the destination Y annotated [0] in red to mark it as the starting vertex of Dijkstra's algorithm with tentative distance zero.</t>
+        </is>
+      </c>
+      <c r="D94" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G94" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H94" s="18" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="B95" s="13" t="n"/>
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>Yakima example after Dijkstra step 2: tentative distances [104] at NB, [96] at MR, [76] at P are recorded in red next to each neighbour of Y; Y still labelled [0]; remaining vertices T, E, A are unlabelled.</t>
+        </is>
+      </c>
+      <c r="D95" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F95" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G95" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H95" s="18" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="B96" s="13" t="n"/>
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>Yakima example after the second iteration: P is the current vertex; E now has tentative distance [172] (via P), and Y is shown struck-through (visited); other labels [104] at NB, [96] at MR, [76] at P remain.</t>
+        </is>
+      </c>
+      <c r="D96" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G96" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="B97" s="13" t="n"/>
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>Yakima example after the third iteration: A has tentative distance [175] (via MR); P and Y appear struck-through (visited); NB still [104], MR [96], E [172].</t>
+        </is>
+      </c>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F97" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G97" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H97" s="18" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="B98" s="13" t="n"/>
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B98" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>Yakima example after the fourth iteration: A's distance is updated to [140] via NB; NB, MR, P, Y all struck-through; E still [172].</t>
+        </is>
+      </c>
+      <c r="D98" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G98" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H98" s="18" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="B99" s="13" t="n"/>
+      <c r="A99" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B99" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>Yakima example after the fifth iteration: T receives tentative distance [160] via A; A, NB, MR, P, Y are struck-through, leaving E [172] still active. The shortest path Y-NB-A-T of 160 minutes is now determined.</t>
+        </is>
+      </c>
+      <c r="D99" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F99" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G99" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H99" s="18" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="B100" s="13" t="n"/>
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>Weighted undirected graph for the Dijkstra example. Seven vertices a-g are joined by edges with weights a-b=2, a-c=6, c-d=8, b-d=5, d-e=10, d-f=15, e-f=6, e-g=2, f-g=6. No vertex is yet marked visited.</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G100" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H100" s="18" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="B101" s="13" t="n"/>
+      <c r="A101" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>Dijkstra step 1: the start vertex a is highlighted in red and labeled with tentative distance 0. Its neighbors b and c receive tentative labels 2 and 6 from a; all other vertices remain labeled infinity.</t>
+        </is>
+      </c>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F101" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G101" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H101" s="18" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="B102" s="13" t="n"/>
+      <c r="A102" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B102" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>Dijkstra step 2: vertex b is now marked as visited with permanent distance 2, and the edge a-b is highlighted in red. Vertex d is updated through b to tentative distance 7. Labels at c, e, f, and g are unchanged.</t>
+        </is>
+      </c>
+      <c r="D102" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G102" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H102" s="18" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="B103" s="13" t="n"/>
+      <c r="A103" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>Dijkstra step 3: vertex c is marked visited with distance 6 and edge a-c is highlighted. Reaching d through c would give 6+8=14, which is worse than the current label 7, so d's tentative distance is unchanged.</t>
+        </is>
+      </c>
+      <c r="D103" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F103" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G103" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H103" s="18" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="B104" s="13" t="n"/>
+      <c r="A104" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>Dijkstra step 4: vertex d is marked visited with distance 7, and the path a-b-d is highlighted in red. Neighbors of d are updated: e to 17 (via 7+10) and f to 22 (via 7+15); g remains infinity.</t>
+        </is>
+      </c>
+      <c r="D104" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F104" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G104" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H104" s="18" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="B105" s="13" t="n"/>
+      <c r="A105" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>Dijkstra step 5: vertex e is marked visited with distance 17 and the edge d-e is added to the highlighted path. From e, vertex g is updated to 17+2=19, improving on its previous infinity label.</t>
+        </is>
+      </c>
+      <c r="D105" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F105" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G105" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H105" s="18" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="B106" s="13" t="n"/>
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B106" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>Dijkstra step 6: vertex g is marked visited with distance 19, and the edge e-g is highlighted, completing a tentative shortest path a-b-d-e-g. The remaining unvisited vertex f keeps tentative distance 22.</t>
+        </is>
+      </c>
+      <c r="D106" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F106" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G106" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H106" s="18" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="B107" s="13" t="n"/>
+      <c r="A107" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
+        <is>
+          <t>Dijkstra step 7: vertex f is marked visited with distance 22 and the edge d-f is highlighted along with the previously found path. All seven vertices are now visited so the algorithm terminates.</t>
+        </is>
+      </c>
+      <c r="D107" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F107" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G107" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H107" s="18" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="B108" s="13" t="n"/>
+      <c r="A108" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>Final state of the Dijkstra example: every vertex carries its shortest-path distance from a (a=0, b=2, c=6, d=7, e=17, g=19, f=22), and the shortest-path tree found by the algorithm is highlighted in red.</t>
+        </is>
+      </c>
+      <c r="D108" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F108" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G108" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H108" s="18" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="B109" s="13" t="n"/>
+      <c r="A109" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>The same seven-vertex weighted graph with the shortest path from a to g highlighted in red: a-b-d-e-g, traversing edges of weight 2, 5, 10, and 2 for a total length of 19.</t>
+        </is>
+      </c>
+      <c r="D109" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F109" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G109" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H109" s="18" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="B110" s="13" t="n"/>
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B110" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>A 4-vertex spanning tree drawn as filled dots at corners of a small region, connected by three edges forming a Y-shape (top-left to top vertex, bottom-right to middle, top to bottom-right), illustrating one possible spanning tree on four vertices.</t>
+        </is>
+      </c>
+      <c r="D110" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F110" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G110" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H110" s="18" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="B111" s="13" t="n"/>
+      <c r="A111" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B111" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>A 4-vertex spanning tree with three edges arranged as a path: middle vertex linked to top-right, top-right linked to bottom-right, and bottom-right linked to bottom-left, showing another spanning-tree configuration on four vertices.</t>
+        </is>
+      </c>
+      <c r="D111" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F111" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G111" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H111" s="18" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="B112" s="13" t="n"/>
+      <c r="A112" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>Composite figure of five small spanning trees with n = 1, 2, 3, 4, 5 vertices arranged left-to-right; each tree has exactly n-1 edges, demonstrating that a spanning tree on n vertices uses n-1 edges.</t>
+        </is>
+      </c>
+      <c r="D112" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G112" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H112" s="18" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="B113" s="13" t="n"/>
+      <c r="A113" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B113" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="inlineStr">
+        <is>
+          <t>Five-vertex graph with cities A, B, C, D, E as black dots, fully connected with dollar-cost edge labels (AB=4, AE=5, AC=8, DC=7, plus higher cross-edges). Edges AB, AE, AC, DC are thick red, marking the MST built by Prim's algorithm starting at A.</t>
+        </is>
+      </c>
+      <c r="D113" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F113" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G113" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H113" s="18" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="B114" s="13" t="n"/>
+      <c r="A114" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B114" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D114" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E114" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F114" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G114" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H114" s="18" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="B115" s="13" t="n"/>
+      <c r="A115" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B115" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D115" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F115" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G115" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H115" s="18" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="B116" s="13" t="n"/>
+      <c r="A116" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>Undirected weighted graph with six yellow circular vertices A, B, C, E, F, G arranged hexagonally. Every pair is joined by an edge labelled with its integer weight (e.g. AB=11, BG=13, AE=14, EF=16, AC=33). Input graph for the Kruskal exercise.</t>
+        </is>
+      </c>
+      <c r="D116" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G116" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="B117" s="13" t="n"/>
+      <c r="A117" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B117" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>Boxed figure for Prim's algorithm: 7-vertex graph with vertices a, b, c, d, e, f, g as red circles. The minimum spanning tree edges d-a, d-f, a-b, b-e, e-c, e-g are drawn thick red; remaining edges are thin black with integer weights.</t>
+        </is>
+      </c>
+      <c r="D117" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F117" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G117" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H117" s="18" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="B118" s="13" t="n"/>
+      <c r="A118" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B118" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>Exercise diagram: a stylized neighborhood shown as six rectangular blocks in two rows of three. Black squares on the inside borders of each block mark houses; students draw edges along the streets the carrier walks to reach every house.</t>
+        </is>
+      </c>
+      <c r="D118" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>David Lippman, Math in Society [CC BY-SA 3.0]. Graphexercise1</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>David Lippman, Math in Society [CC BY-SA 3.0], “Graphexercise1”, CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="G118" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H118" s="18" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="B119" s="13" t="n"/>
+      <c r="A119" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B119" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>Exercise map of a fictional town: a teal river divides the area into several land masses, with seven black bars marking bridges. Students convert the map to a graph to test for an Eulerian path crossing each bridge once.</t>
+        </is>
+      </c>
+      <c r="D119" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="E119" s="18" t="inlineStr">
+        <is>
+          <t>David Lippman, Math in Society [CC BY-SA 3.0]. Graphexercise2</t>
+        </is>
+      </c>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>David Lippman, Math in Society [CC BY-SA 3.0], “Graphexercise2”, CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="G119" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H119" s="18" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="B120" s="13" t="n"/>
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>Seven-vertex weighted graph for the shortest-path exercise. Vertices A, B, C, D, E, F, G in a roughly diamond layout with integer edge weights (AB=1, AC=4, BD=3, CD=2, DE=2, DF=4, EG=7, FG=6, plus chords). Goal: find the shortest path from A to G.</t>
+        </is>
+      </c>
+      <c r="D120" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G120" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H120" s="18" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="B121" s="13" t="n"/>
+      <c r="A121" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B121" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="inlineStr">
+        <is>
+          <t>Airfare table giving one-way dollar fares between Seattle, Honolulu, London, Moscow, and Cairo (e.g. Seattle-Honolulu $159, Honolulu-London $830, London-Moscow $245, Moscow-Cairo $329). Used as input for building a weighted graph.</t>
+        </is>
+      </c>
+      <c r="D121" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E121" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F121" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G121" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H121" s="18" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="B122" s="13" t="n"/>
+      <c r="A122" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B122" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>Small undirected graph with five black-dot vertices arranged in two rows, with four edges (square plus a diagonal extension). One of three example graphs presented side-by-side asking 'Which of these graphs are connected?'.</t>
+        </is>
+      </c>
+      <c r="D122" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E122" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G122" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H122" s="18" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="B123" s="13" t="n"/>
+      <c r="A123" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B123" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="inlineStr">
+        <is>
+          <t>Small undirected graph with five black-dot vertices; edges form one triangle on the right plus a separate vertical segment on the left, leaving the graph in two components. One of three connectivity examples.</t>
+        </is>
+      </c>
+      <c r="D123" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E123" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F123" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G123" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H123" s="18" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="B124" s="13" t="n"/>
+      <c r="A124" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B124" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>Small undirected graph with five black-dot vertices fully linked through a series of edges so all vertices belong to one component. The third option in the 'Which of these graphs are connected?' exercise.</t>
+        </is>
+      </c>
+      <c r="D124" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E124" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F124" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G124" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H124" s="18" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="B125" s="13" t="n"/>
+      <c r="A125" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B125" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="inlineStr">
+        <is>
+          <t>Eight-vertex graph drawn on a 3-by-3 grid layout with three short horizontal segments stacked at top, middle, and bottom; the components are not all linked, illustrating a disconnected graph for the second connectivity question.</t>
+        </is>
+      </c>
+      <c r="D125" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F125" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G125" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H125" s="18" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="B126" s="13" t="n"/>
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>Eight-vertex graph on a 3-by-3 grid layout where a central vertex (1.5,1) has high degree, connecting most of the graph; one corner pair remains separated. Used for the second 'Which of these graphs are connected?' question.</t>
+        </is>
+      </c>
+      <c r="D126" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E126" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G126" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H126" s="18" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="B127" s="13" t="n"/>
+      <c r="A127" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B127" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
+        <is>
+          <t>Eight-vertex graph with edges forming a connected outer cycle plus several interior diagonals; the third option in the second connectivity exercise.</t>
+        </is>
+      </c>
+      <c r="D127" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E127" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F127" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G127" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H127" s="18" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="B128" s="13" t="n"/>
+      <c r="A128" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B128" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D128" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E128" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F128" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G128" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H128" s="18" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="B129" s="13" t="n"/>
+      <c r="A129" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B129" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="inlineStr">
+        <is>
+          <t>Weighted graph on five labelled vertices A, B, C, D, E in a pentagonal layout, fully connected by ten edges with dollar-cost labels (e.g. CD=$5.6, CA=$5.1, BC=$4.3, AE=$4.4, CE=$4.0); used to plan a minimum-cost sonet ring.</t>
+        </is>
+      </c>
+      <c r="D129" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E129" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F129" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G129" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H129" s="18" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="B130" s="13" t="n"/>
+      <c r="A130" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 14)</t>
+        </is>
+      </c>
+      <c r="B130" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D130" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E130" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G130" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H130" s="18" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="B131" s="13" t="n"/>
+      <c r="A131" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 15)</t>
+        </is>
+      </c>
+      <c r="B131" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
+          <t>Plot of a piecewise linear function composed of several line segments with breakpoints marked on the horizontal axis.</t>
+        </is>
+      </c>
+      <c r="D131" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E131" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F131" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G131" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H131" s="18" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="B132" s="13" t="n"/>
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 15)</t>
+        </is>
+      </c>
+      <c r="B132" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>Gantt chart showing a job shop scheduling solution with three machines processing five jobs over time. Colored horizontal bars represent job operations on each machine, demonstrating how jobs are sequenced to minimize makespan.</t>
+        </is>
+      </c>
+      <c r="D132" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G132" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H132" s="18" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="B133" s="13" t="n"/>
+      <c r="A133" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 15)</t>
+        </is>
+      </c>
+      <c r="B133" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="inlineStr">
+        <is>
+          <t>Gantt chart showing a Job Shop Scheduling Problem solution with three machines and four jobs represented by colored bars over a time horizon of 0 to 12 units.</t>
+        </is>
+      </c>
+      <c r="D133" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E133" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F133" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G133" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H133" s="18" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="B134" s="13" t="n"/>
+      <c r="A134" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 15)</t>
+        </is>
+      </c>
+      <c r="B134" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>Photograph of colorful Duplo building blocks arranged on a table, representing a physical demonstration of a job shop scheduling problem with blocks of different colors and sizes.</t>
+        </is>
+      </c>
+      <c r="D134" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G134" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H134" s="18" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="B135" s="13" t="n"/>
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 2)</t>
+        </is>
+      </c>
+      <c r="B135" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
+        <is>
+          <t>Schematic of a two-period production planning network: two gray circles labelled 1 and 2. Up-arrows show production x_1, x_2; down-arrows show demands 10 and 4; horizontal arrows show inventory s_0 in, s_1 between nodes, s_2 out. Rows labelled Production, Inventory, Demand.</t>
+        </is>
+      </c>
+      <c r="D135" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E135" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G135" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H135" s="18" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="B136" s="13" t="n"/>
+      <c r="A136" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 3)</t>
+        </is>
+      </c>
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="inlineStr">
+        <is>
+          <t>Excel spreadsheet showing the recommended Solver layout: data cells (coefficients, right-hand sides) shaded light blue, decision-variable cells shaded yellow, and formula cells (objective and constraint sums) shaded light green.</t>
+        </is>
+      </c>
+      <c r="D136" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G136" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H136" s="18" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="B137" s="13" t="n"/>
+      <c r="A137" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 3)</t>
+        </is>
+      </c>
+      <c r="B137" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="inlineStr">
+        <is>
+          <t>Screenshot of Excel's Data ribbon with the Solver button highlighted on the right side of the toolbar, showing where to click to launch the Solver Parameters dialog after enabling the add-in.</t>
+        </is>
+      </c>
+      <c r="D137" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E137" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F137" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G137" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H137" s="18" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="B138" s="13" t="n"/>
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 3)</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>Solver Parameters dialog with fields filled in: Set Objective cell, Max/Min selector, By Changing Variable Cells range, Subject to the Constraints list, and the Make Unconstrained Variables Non-Negative checkbox enabled.</t>
+        </is>
+      </c>
+      <c r="D138" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H138" s="18" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="B139" s="13" t="n"/>
+      <c r="A139" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 3)</t>
+        </is>
+      </c>
+      <c r="B139" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="inlineStr">
+        <is>
+          <t>Close-up of the Select a Solving Method dropdown in the Solver Parameters dialog, showing the three options GRG Nonlinear, Simplex LP, and Evolutionary that the user picks based on whether the problem is smooth nonlinear, linear, or non-smooth/integer.</t>
+        </is>
+      </c>
+      <c r="D139" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E139" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F139" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G139" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H139" s="18" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="B140" s="13" t="n"/>
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 3)</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>Solver Results dialog that appears after solving, offering Keep Solver Solution or Restore Original Values, with a Reports list (Answer, Sensitivity, Limits) on the right that the user can select to generate diagnostic reports.</t>
+        </is>
+      </c>
+      <c r="D140" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F140" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G140" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H140" s="18" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="B141" s="13" t="n"/>
+      <c r="A141" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 3)</t>
+        </is>
+      </c>
+      <c r="B141" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="inlineStr">
+        <is>
+          <t>Excel Answer Report worksheet generated by Solver, listing the objective cell's original and final values, a table of variable cells with their final values, and a constraints table showing each constraint's cell value, formula, status (Binding or Not Binding), and slack.</t>
+        </is>
+      </c>
+      <c r="D141" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E141" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F141" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G141" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H141" s="18" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="B142" s="13" t="n"/>
+      <c r="A142" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 3)</t>
+        </is>
+      </c>
+      <c r="B142" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>Excel Sensitivity Report worksheet with a Variable Cells table (final value, reduced cost, objective coefficient, allowable increase/decrease) and a Constraints table (shadow price, right-hand side, allowable increase/decrease) for each decision variable and constraint.</t>
+        </is>
+      </c>
+      <c r="D142" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F142" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G142" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H142" s="18" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="B143" s="13" t="n"/>
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 3)</t>
+        </is>
+      </c>
+      <c r="B143" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
+        <is>
+          <t>Excel spreadsheet after Solver has run, with the yellow variable cells now populated with optimal decision-variable values and the green formula cells displaying the resulting objective value and constraint sums, illustrating the final optimized layout.</t>
+        </is>
+      </c>
+      <c r="D143" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E143" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F143" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G143" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H143" s="18" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="B144" s="13" t="n"/>
+      <c r="A144" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 4)</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>Schematic of a multi-period production network: gray circles labelled 1, 2, ..., T-1, T. Up-arrows show production x_t; down-arrows show demand d_t; horizontal arrows show inventory s_0 in, s_1, ..., s_{T-1} between nodes, s_T out. Rows labelled Production, Inventory, Demand.</t>
+        </is>
+      </c>
+      <c r="D144" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G144" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H144" s="18" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="B145" s="13" t="n"/>
+      <c r="A145" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 4)</t>
+        </is>
+      </c>
+      <c r="B145" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="inlineStr">
+        <is>
+          <t>Bipartite assignment diagram: three people P1, P2, P3 drawn as stick-figure icons in blue circles on the left and three tasks T1, T2, T3 drawn as clipboard icons in red squares on the right, with lines connecting every person to every task.</t>
+        </is>
+      </c>
+      <c r="D145" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E145" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F145" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G145" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H145" s="18" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="B146" s="13" t="n"/>
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 4)</t>
+        </is>
+      </c>
+      <c r="B146" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="inlineStr">
+        <is>
+          <t>Undirected network with six numbered circular nodes: edges join 6-4, 4-5, 4-3, 5-1, 5-2, 3-2, and 2-1.</t>
+        </is>
+      </c>
+      <c r="D146" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F146" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G146" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H146" s="18" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="B147" s="13" t="n"/>
+      <c r="A147" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 4)</t>
+        </is>
+      </c>
+      <c r="B147" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
+        <is>
+          <t>Directed version of the same six-node network: curved arrows show arc directions, including a two-way pair of arcs between nodes 6 and 4 and a cycle through nodes 5, 1, 2, and 3.</t>
+        </is>
+      </c>
+      <c r="D147" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E147" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G147" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H147" s="18" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="B148" s="13" t="n"/>
+      <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 4)</t>
+        </is>
+      </c>
+      <c r="B148" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="inlineStr">
+        <is>
+          <t>Transshipment network: supply nodes W1 (+30) and W2 (+20) on the left, transshipment nodes D1 and D2 in the middle, and demand nodes S1 (-20), S2 (-15), S3 (-15) on the right. Arcs are labeled with unit costs: W1 to D1 costs 4, W1 to D2 costs 6, W2 to D1 costs 5, W2 to D2 costs 4, D1 to S1 costs 2, D1 to S2 costs 3, D2 to S2 costs 1, and D2 to S3 costs 2.</t>
+        </is>
+      </c>
+      <c r="D148" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E148" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F148" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G148" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H148" s="18" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="B149" s="13" t="n"/>
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 4)</t>
+        </is>
+      </c>
+      <c r="B149" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="inlineStr">
+        <is>
+          <t>Directed network with eight nodes labeled a through h arranged left to right. Blue numbers give node supplies (+10 at a, -5 at b, +5 at d, 0 at c and e, -5 at g and h) and red numbers on the arcs give unit costs.</t>
+        </is>
+      </c>
+      <c r="D149" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E149" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F149" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G149" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H149" s="18" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="B150" s="13" t="n"/>
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 4)</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
+        <is>
+          <t>Disaster-relief transportation network: warehouse rectangles W1-W5 (inventories 200, 300, 150, 250, 180), distribution circles D1, D2, D3, and a central diamond Hub. Directed arcs labelled with capacities route supplies through distribution centers to the Hub.</t>
+        </is>
+      </c>
+      <c r="D150" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F150" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G150" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H150" s="18" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="B151" s="13" t="n"/>
+      <c r="A151" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 4)</t>
+        </is>
+      </c>
+      <c r="B151" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="inlineStr">
+        <is>
+          <t>Directed max-flow exercise network: green source s and red sink t with intermediate nodes v1, v2, v3, v4. Arc capacities: s to v1 is 11, s to v2 is 8, between v1 and v2 are 10 and 1, v1 to v3 is 12, v3 to v2 is 4, v4 to v3 is 7, v2 to v4 is 11, v3 to t is 15, v4 to t is 4.</t>
+        </is>
+      </c>
+      <c r="D151" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E151" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F151" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G151" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H151" s="18" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="B152" s="13" t="n"/>
+      <c r="A152" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 4)</t>
+        </is>
+      </c>
+      <c r="B152" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>Six-node directed network for a min-cost flow exercise: nodes v1 through v6 with blue supply values (6 at v1, -5 at v2, -3 at v3, -6 at v4, -2 at v5, 10 at v6). Each arc shows its capacity in black and a red cost value, for example v5 to v1 has capacity 11 and cost 4.</t>
+        </is>
+      </c>
+      <c r="D152" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E152" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F152" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G152" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H152" s="18" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="B153" s="13" t="n"/>
+      <c r="A153" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 5)</t>
+        </is>
+      </c>
+      <c r="B153" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
+        <is>
+          <t>Cone-shaped feasible region on x1-x2 axes: blue shading between the lines s1 = 0 (red, lower boundary) and s3 = 0 (orange, upper boundary), with the line s2 = 0 (teal) crossing above; red square markers sit at (0,0), (0,1), and (2,3).</t>
+        </is>
+      </c>
+      <c r="D153" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E153" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G153" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H153" s="18" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="B154" s="13" t="n"/>
+      <c r="A154" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 5)</t>
+        </is>
+      </c>
+      <c r="B154" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>The same cone-shaped region between s1 = 0 and s3 = 0 with s2 = 0 above, shaded blue and marked with red squares at (0,0), (0,1), and (2,3), used to discuss which basic solutions are feasible.</t>
+        </is>
+      </c>
+      <c r="D154" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F154" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G154" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H154" s="18" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="B155" s="13" t="n"/>
+      <c r="A155" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 5)</t>
+        </is>
+      </c>
+      <c r="B155" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C155" s="18" t="inlineStr">
+        <is>
+          <t>Recession cone plot: shaded blue cone between the lines s1 = 0 (red) and s3 = 0 (orange) with s2 = 0 (teal) above; the normalization line x1 + x2 = 1 is drawn crossing the cone near the origin.</t>
+        </is>
+      </c>
+      <c r="D155" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E155" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F155" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G155" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H155" s="18" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="B156" s="13" t="n"/>
+      <c r="A156" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 5)</t>
+        </is>
+      </c>
+      <c r="B156" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="inlineStr">
+        <is>
+          <t>The same recession cone between s1 = 0 and s3 = 0 with the line x1 + x2 = 1 crossing it, used to identify the extreme rays of the cone.</t>
+        </is>
+      </c>
+      <c r="D156" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F156" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H156" s="18" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="B157" s="13" t="n"/>
+      <c r="A157" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 5)</t>
+        </is>
+      </c>
+      <c r="B157" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="inlineStr">
+        <is>
+          <t>Zoomed view of the normalization segment: the line x1 + x2 = 1 crosses the shaded cone between s1 = 0 and s3 = 0, and two red square points mark where the extreme rays meet the line.</t>
+        </is>
+      </c>
+      <c r="D157" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E157" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F157" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G157" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H157" s="18" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="B158" s="13" t="n"/>
+      <c r="A158" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 6)</t>
+        </is>
+      </c>
+      <c r="B158" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D158" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E158" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F158" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G158" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H158" s="18" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="B159" s="13" t="n"/>
+      <c r="A159" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 6)</t>
+        </is>
+      </c>
+      <c r="B159" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>Two side-by-side shapes contrasting a convex set (a tilted gray ellipse) with a non-convex set (a curvy gray blob with a notch); a chord between two interior dots leaves the second shape, demonstrating non-convexity.</t>
+        </is>
+      </c>
+      <c r="D159" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E159" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F159" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G159" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H159" s="18" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="B160" s="13" t="n"/>
+      <c r="A160" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 6)</t>
+        </is>
+      </c>
+      <c r="B160" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D160" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E160" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F160" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H160" s="18" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="B161" s="13" t="n"/>
+      <c r="A161" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 6)</t>
+        </is>
+      </c>
+      <c r="B161" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D161" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E161" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F161" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G161" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H161" s="18" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="B162" s="13" t="n"/>
+      <c r="A162" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 6)</t>
+        </is>
+      </c>
+      <c r="B162" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
+        <is>
+          <t>One-dimensional number line showing c^T z between c^T x and c^T y. Three dots mark min and max of {c^T x, c^T y} and the convex combination c^T z = lambda c^T x + (1-lambda) c^T y in between.</t>
+        </is>
+      </c>
+      <c r="D162" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E162" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F162" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G162" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H162" s="18" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="B163" s="13" t="n"/>
+      <c r="A163" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 6)</t>
+        </is>
+      </c>
+      <c r="B163" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>Two-dimensional plot of a quadrilateral polytope with vertices (0,0), (1,2), (3,2), (4,0). A green vertex v and two interior red points x and y each show short arrows v +/- epsilon*d, distinguishing perturbations that stay inside from those that leave the polytope.</t>
+        </is>
+      </c>
+      <c r="D163" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E163" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F163" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G163" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H163" s="18" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="B164" s="13" t="n"/>
+      <c r="A164" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 6)</t>
+        </is>
+      </c>
+      <c r="B164" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D164" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E164" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F164" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G164" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H164" s="18" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="B165" s="13" t="n"/>
+      <c r="A165" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B165" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D165" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E165" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F165" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G165" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H165" s="18" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="B166" s="13" t="n"/>
+      <c r="A166" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B166" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type  of Constraint  </t>
+        </is>
+      </c>
+      <c r="D166" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E166" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F166" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G166" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H166" s="18" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="B167" s="13" t="n"/>
+      <c r="A167" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B167" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Form  of Constraint  </t>
+        </is>
+      </c>
+      <c r="D167" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E167" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F167" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G167" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H167" s="18" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="B168" s="13" t="n"/>
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B168" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C168" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                      Constraint in                                                       Augmented  Form  </t>
+        </is>
+      </c>
+      <c r="D168" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E168" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F168" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G168" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H168" s="18" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="B169" s="13" t="n"/>
+      <c r="A169" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B169" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                                                                                            Constraint                                                                                                                             Boundary Eq.  </t>
+        </is>
+      </c>
+      <c r="D169" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E169" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F169" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G169" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H169" s="18" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="B170" s="13" t="n"/>
+      <c r="A170" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B170" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                                                                                                                                                                  Indicating                                                                                                                                                                                                   Variable(s)  </t>
+        </is>
+      </c>
+      <c r="D170" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E170" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F170" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G170" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H170" s="18" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="B171" s="13" t="n"/>
+      <c r="A171" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B171" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
+        <is>
+          <t>A 2D feasible polytope shaded as a convex polygon with several vertices marked; illustrates that the simplex method walks along edges from vertex to vertex of such a region in search of an optimum.</t>
+        </is>
+      </c>
+      <c r="D171" s="18" t="inlineStr">
+        <is>
+          <t>CC BY 3.0 US</t>
+        </is>
+      </c>
+      <c r="E171" s="18" t="inlineStr">
+        <is>
+          <t>Foundations of Applied Mathematics labs, Brigham Young University</t>
+        </is>
+      </c>
+      <c r="F171" s="18" t="inlineStr">
+        <is>
+          <t>Humpherys, Jarvis, et al., Foundations of Applied Mathematics, CC BY 3.0 US, https://github.com/Foundations-of-Applied-Mathematics</t>
+        </is>
+      </c>
+      <c r="G171" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H171" s="18" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="B172" s="13" t="n"/>
+      <c r="A172" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B172" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D172" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E172" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F172" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G172" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H172" s="18" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="B173" s="13" t="n"/>
+      <c r="A173" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B173" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D173" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E173" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F173" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G173" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H173" s="18" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="B174" s="13" t="n"/>
+      <c r="A174" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B174" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D174" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E174" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F174" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G174" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H174" s="18" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="B175" s="13" t="n"/>
+      <c r="A175" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B175" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D175" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E175" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F175" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G175" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H175" s="18" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="B176" s="13" t="n"/>
+      <c r="A176" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B176" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D176" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E176" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F176" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G176" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H176" s="18" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="B177" s="13" t="n"/>
+      <c r="A177" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B177" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D177" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E177" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F177" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G177" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H177" s="18" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="B178" s="13" t="n"/>
+      <c r="A178" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B178" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
+        <is>
+          <t>Diagram from this section of the textbook (see surrounding text for description).</t>
+        </is>
+      </c>
+      <c r="D178" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E178" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib/screenshot).</t>
+        </is>
+      </c>
+      <c r="F178" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G178" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H178" s="18" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="B179" s="13" t="n"/>
+      <c r="A179" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B179" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>Desmos plot of the feasible region defined by x1-x2&lt;=1, 2x1-x2&lt;=3, x1,x2&gt;=0: an unbounded region extending to the right in the first quadrant, illustrating the unbounded LP example.</t>
+        </is>
+      </c>
+      <c r="D179" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E179" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F179" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G179" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H179" s="18" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="B180" s="13" t="n"/>
+      <c r="A180" s="18" t="inlineStr">
+        <is>
+          <t>unnumbered (Ch. 7)</t>
+        </is>
+      </c>
+      <c r="B180" s="18" t="inlineStr">
+        <is>
+          <t>(no caption; appears inline in the text)</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="inlineStr">
+        <is>
+          <t>Desmos graph of a 2-variable LP feasible region with vertices labeled A, B, C, D used to identify basic and nonbasic variables and to trace pivot moves between adjacent basic feasible solutions.</t>
+        </is>
+      </c>
+      <c r="D180" s="18" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0 (original figure created for this book)</t>
+        </is>
+      </c>
+      <c r="E180" s="18" t="inlineStr">
+        <is>
+          <t>Original figure by the book authors (TikZ/matplotlib).</t>
+        </is>
+      </c>
+      <c r="F180" s="18" t="inlineStr">
+        <is>
+          <t>N/A (original work)</t>
+        </is>
+      </c>
+      <c r="G180" s="18" t="inlineStr">
+        <is>
+          <t>Inline image without a numbered caption.</t>
+        </is>
+      </c>
+      <c r="H180" s="18" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="B181" s="13" t="n"/>
